--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-19T19:00:06.925Z</t>
+    <t>2026-10-19T19:21:48.135Z</t>
   </si>
   <si>
     <t>Das grösste Automobilunternehmen der Schweiz | AMAG</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-19T19:21:48.135Z</t>
+    <t>2026-10-20T11:44:12.985Z</t>
   </si>
   <si>
     <t>Das grösste Automobilunternehmen der Schweiz | AMAG</t>
@@ -61,6 +61,27 @@
     <t>https://www.amag.ch/de.html</t>
   </si>
   <si>
+    <t>de/service.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","hero-split","video-brand-film","long-form-article","icon-text-box","service-offer","image-text-card","accordion-faq","accordion-faq","accordion-faq","accordion-faq","news-cards","pledge-row","garage-chooser","cta-band","newsletter-band","direct-entry"]</t>
+  </si>
+  <si>
+    <t>de/service</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>2026-10-20T08:57:28.188Z</t>
+  </si>
+  <si>
+    <t>Alle Fahrzeug-Services im Überblick | AMAG</t>
+  </si>
+  <si>
+    <t>https://www.amag.ch/de/service.html</t>
+  </si>
+  <si>
     <t>de/garagenuebersicht/garage-buelach.report.json</t>
   </si>
   <si>
@@ -73,13 +94,34 @@
     <t>garagenuebersicht</t>
   </si>
   <si>
-    <t>2026-10-19T18:54:50.583Z</t>
+    <t>2026-10-19T19:25:35.350Z</t>
   </si>
   <si>
     <t>🚗 Autohändler und Garage Bülach | AMAG</t>
   </si>
   <si>
     <t>https://www.amag.ch/de/garagenuebersicht/garage-buelach.html</t>
+  </si>
+  <si>
+    <t>de/komponenten/storelocator.report.json</t>
+  </si>
+  <si>
+    <t>["dealer-search"]</t>
+  </si>
+  <si>
+    <t>de/komponenten/storelocator</t>
+  </si>
+  <si>
+    <t>storelocator</t>
+  </si>
+  <si>
+    <t>2026-10-20T07:34:42.502Z</t>
+  </si>
+  <si>
+    <t>Finden Sie Ihre AMAG Garage</t>
+  </si>
+  <si>
+    <t>https://www.amag.ch/de/komponenten/storelocator.html</t>
   </si>
 </sst>
 </file>
@@ -468,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
@@ -557,6 +599,58 @@
         <v>22</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
